--- a/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,8</t>
+          <t>-6,15; 5,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 6,65</t>
+          <t>-5,87; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,78</t>
+          <t>-1,76; 9,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 6,03</t>
+          <t>-7,43; 7,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,44</t>
+          <t>-6,51; 5,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 7,89</t>
+          <t>-6,35; 8,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 11,33</t>
+          <t>-1,9; 11,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 7,0</t>
+          <t>-7,99; 8,34</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,45</t>
+          <t>-1,52; 9,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,47</t>
+          <t>-5,27; 4,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,65</t>
+          <t>-3,77; 4,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,86</t>
+          <t>-1,69; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 11,67</t>
+          <t>-1,76; 12,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,05</t>
+          <t>-5,77; 4,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 5,12</t>
+          <t>-4,0; 4,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 10,25</t>
+          <t>-1,76; 9,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,77</t>
+          <t>-7,91; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 4,28</t>
+          <t>-5,61; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 9,56</t>
+          <t>-0,27; 9,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 8,1</t>
+          <t>-4,93; 7,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,9</t>
+          <t>-8,32; 2,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,82</t>
+          <t>-6,03; 5,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 11,13</t>
+          <t>-0,22; 11,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 9,66</t>
+          <t>-5,48; 8,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,7</t>
+          <t>-6,22; 4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,96</t>
+          <t>-6,2; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,38</t>
+          <t>-3,6; 5,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 1,87</t>
+          <t>-12,95; 1,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,2</t>
+          <t>-6,73; 5,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,25</t>
+          <t>-6,56; 3,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 6,02</t>
+          <t>-3,78; 6,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 2,36</t>
+          <t>-14,82; 2,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,81</t>
+          <t>-2,93; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,82</t>
+          <t>-3,19; 2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,45</t>
+          <t>-0,29; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,84</t>
+          <t>-3,25; 3,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,21</t>
+          <t>-3,22; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,04</t>
+          <t>-3,47; 2,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,0</t>
+          <t>-0,3; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,3</t>
+          <t>-3,64; 3,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,11</t>
+          <t>-6,09; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 7,06</t>
+          <t>-5,05; 7,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 9,81</t>
+          <t>-2,15; 9,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 7,01</t>
+          <t>-6,45; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,78</t>
+          <t>-6,51; 5,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 8,45</t>
+          <t>-5,5; 9,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 11,33</t>
+          <t>-2,23; 11,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 8,34</t>
+          <t>-6,96; 8,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 9,55</t>
+          <t>-2,38; 9,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,01</t>
+          <t>-4,95; 4,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,35</t>
+          <t>-3,81; 4,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,45</t>
+          <t>-1,32; 8,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 12,17</t>
+          <t>-2,46; 11,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,58</t>
+          <t>-5,42; 4,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,77</t>
+          <t>-4,04; 4,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 9,92</t>
+          <t>-1,46; 9,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,19</t>
+          <t>-8,4; 2,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 5,3</t>
+          <t>-6,4; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 9,53</t>
+          <t>-0,45; 9,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 7,35</t>
+          <t>-4,97; 7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 2,38</t>
+          <t>-8,86; 2,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 5,99</t>
+          <t>-6,83; 5,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 11,08</t>
+          <t>-0,47; 10,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 8,64</t>
+          <t>-5,49; 9,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,41</t>
+          <t>-6,6; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 3,18</t>
+          <t>-6,2; 3,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,65</t>
+          <t>-3,97; 5,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,66</t>
+          <t>-12,34; 2,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,06</t>
+          <t>-7,15; 4,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,5</t>
+          <t>-6,51; 3,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,34</t>
+          <t>-4,22; 6,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 2,1</t>
+          <t>-14,46; 2,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,51</t>
+          <t>-2,66; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,24</t>
+          <t>-3,37; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,47</t>
+          <t>-0,34; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,26</t>
+          <t>-3,24; 3,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,83</t>
+          <t>-2,95; 3,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,52</t>
+          <t>-3,65; 2,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,04</t>
+          <t>-0,37; 5,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,77</t>
+          <t>-3,68; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,49%</t>
+          <t>-0,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 4,83</t>
+          <t>-6,17; 4,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 7,99</t>
+          <t>-5,67; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 9,56</t>
+          <t>-2,34; 9,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 7,24</t>
+          <t>-8,04; 6,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,46</t>
+          <t>-6,64; 5,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 9,46</t>
+          <t>-6,2; 7,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 11,1</t>
+          <t>-2,51; 11,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 8,45</t>
+          <t>-8,64; 7,07</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,33</t>
+          <t>-1,97; 9,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,35</t>
+          <t>-5,4; 4,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,22</t>
+          <t>-3,43; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,16</t>
+          <t>-1,74; 8,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 11,74</t>
+          <t>-2,28; 11,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,96</t>
+          <t>-5,86; 5,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,74</t>
+          <t>-3,62; 5,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 9,49</t>
+          <t>-1,86; 10,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>-0,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 2,03</t>
+          <t>-7,97; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,68</t>
+          <t>-6,82; 4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 9,38</t>
+          <t>-0,31; 9,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 7,92</t>
+          <t>-5,56; 5,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 2,25</t>
+          <t>-8,45; 1,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 5,29</t>
+          <t>-7,23; 4,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 10,83</t>
+          <t>-0,38; 11,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 9,29</t>
+          <t>-6,13; 7,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,15%</t>
+          <t>-6,1%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,19</t>
+          <t>-6,75; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 3,38</t>
+          <t>-6,58; 2,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,94</t>
+          <t>-3,97; 5,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 2,19</t>
+          <t>-13,18; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 4,8</t>
+          <t>-7,23; 4,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,69</t>
+          <t>-6,97; 3,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,69</t>
+          <t>-4,18; 6,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 2,64</t>
+          <t>-15,13; 2,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,2%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,69</t>
+          <t>-2,92; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,0</t>
+          <t>-3,24; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,7</t>
+          <t>-0,36; 4,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,13</t>
+          <t>-4,32; 2,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,09</t>
+          <t>-3,27; 3,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,23</t>
+          <t>-3,53; 2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,25</t>
+          <t>-0,34; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,65</t>
+          <t>-4,8; 2,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-0,67%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.547024779164651</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5725893875259347</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.814904740395919</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.6038158938905691</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.005999093450577292</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.006435461004195409</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.0424582894171323</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.006707867529607539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,17; 4,8</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,67; 6,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 9,78</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,04; 6,22</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-6,64; 5,44</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-6,2; 7,89</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-2,51; 11,33</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 7,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.172421587819301</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.665916778039272</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.34312065163058</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.037491338194174</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.06635733725317688</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.0620005123927172</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.02505081947224139</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.08635926061311967</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.795498027790731</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.653379681003309</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.777155409542825</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.216414837339124</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.05444953293481044</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.07887397545791783</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1132837279197045</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.0707267036388237</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-0,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 9,45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,4; 4,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 4,65</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 8,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 11,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,86; 5,05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 5,12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 10,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.676765768915191</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.434773828588797</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2902167306190639</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.299622595160012</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04425159313619229</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.004836351653611651</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.003138275058626093</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.03689655842413098</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,45%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.973872670128062</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.395160656455537</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.427649292699456</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.744335768599237</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.02276204398349213</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05860963729780547</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03621720997328287</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.01859075167243197</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,97; 1,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,82; 4,28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 9,56</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,56; 5,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-8,45; 1,9</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,82</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 11,13</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-6,13; 7,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.447367016381977</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.465248546937763</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.650816945897644</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.609087566224192</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1166960802587828</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05048576040694597</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.05119013587607215</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1013958403360831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,1%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.893864688083891</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7015189475388928</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.300548341818155</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.3944806709394011</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.03105440533221717</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.007706220200837792</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.0476922238450336</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.004453448808179495</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 3,7</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,58; 2,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 5,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,18; 2,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-6,97; 3,25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-4,18; 6,02</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-15,13; 2,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.97390042504706</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.820433903812886</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.310797394963326</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.560527269200696</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.08448585227775141</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07233158956734481</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.003827145337763443</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.06131874800157742</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.770056974759521</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.281810813935421</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.564620325691212</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.987442845655372</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.01901957765928655</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.04821305055150992</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1113304282842357</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.07170870768644752</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.298490503845984</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.550250364177319</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8954179702777232</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.10080783027107</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01442939682558445</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01661552258488877</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.009777844063583827</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.06097847704324341</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.746895390575522</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.578677026232574</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.970301174474439</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.18047286491055</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07233858347317426</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.06968704695125154</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.04181928418140506</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1513013654211601</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.699411294740322</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.962755644909322</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.378242514114118</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.212117027698629</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04198989566711038</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.03254737690864019</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06023095254620032</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.02699686238262918</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 2,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,24; 1,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 4,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 2,22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 3,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 2,04</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 5,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-4,8; 2,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.01641568973587137</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.572213631835139</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.04432851766766</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.7412044644342974</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.0001848168092523929</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.006294542833068484</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.02241949120713237</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.008429588878299641</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.922927534006437</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.236555473797076</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.359802305542555</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.320230565958391</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.03272426545965557</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.03527398787287953</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.003430869012643234</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.04798518101580782</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.806071217579716</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.822270207537349</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.449262631310874</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.219703258389621</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03212272690997615</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0203661959940989</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.04995044099371614</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.02632751823094234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
